--- a/usecases/uc-06-vm-lifecycle/TCS-Agentic-AI-UC06-VM-Lifecycle.xlsx
+++ b/usecases/uc-06-vm-lifecycle/TCS-Agentic-AI-UC06-VM-Lifecycle.xlsx
@@ -25,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="423">
   <si>
     <t>TCS Agentic AI — Governed VM Provisioning &amp; Lifecycle  ·  UC-06</t>
   </si>
   <si>
     <t>One sentence in. A governed, owned, accountable virtual machine out — and an agent that remembers why it built it.</t>
+  </si>
+  <si>
+    <t>SCOPE  ·  VMs BORN on OpenShift Virtualization — requested, provisioned, right-sized, reclaimed.   Machines arriving FROM VMware are UC-10, VM Migration Assurance.</t>
   </si>
   <si>
     <t>Attribute</t>
@@ -1319,14 +1322,14 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10.5"/>
+      <color rgb="FF1E293B"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1442,12 +1445,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1532,15 +1535,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1936,7 +1939,7 @@
   <sheetPr>
     <tabColor rgb="FF2563EB"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1955,121 +1958,126 @@
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+    </row>
+    <row r="6" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7" t="s">
+    </row>
+    <row r="7" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="5" t="s">
+    </row>
+    <row r="8" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7" t="s">
+    </row>
+    <row r="9" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5" t="s">
+    </row>
+    <row r="10" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="7" t="s">
+    </row>
+    <row r="11" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="5" t="s">
+    </row>
+    <row r="12" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="7" t="s">
+    </row>
+    <row r="13" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="B13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="5" t="s">
+    </row>
+    <row r="14" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="7" t="s">
+    </row>
+    <row r="15" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="5" t="s">
+    </row>
+    <row r="16" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="7" t="s">
+    </row>
+    <row r="17" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="8"/>
+    </row>
+    <row r="18" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2090,101 +2098,101 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>248</v>
       </c>
+      <c r="B3" s="4" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>249</v>
+      <c r="A4" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>252</v>
+      <c r="A6" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>76</v>
+      <c r="A8" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>259</v>
+      <c r="A10" s="3" t="s">
+        <v>260</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>263</v>
+      <c r="A12" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B14" s="12"/>
     </row>
@@ -2213,102 +2221,102 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
+      <c r="A3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>270</v>
+      <c r="A4" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>276</v>
+      <c r="A6" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>282</v>
+      <c r="A8" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>288</v>
+      <c r="A10" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -2337,135 +2345,135 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>295</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2495,124 +2503,124 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>198</v>
+      <c r="B3" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>330</v>
+      <c r="A4" s="3" t="s">
+        <v>331</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>336</v>
+      <c r="A6" s="3" t="s">
+        <v>337</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>342</v>
+      <c r="A8" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>348</v>
+      <c r="A10" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>354</v>
+      <c r="A12" s="3" t="s">
+        <v>355</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
@@ -2642,185 +2650,185 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>49</v>
+      <c r="B3" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>361</v>
+      <c r="A4" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>367</v>
+      <c r="A6" s="3" t="s">
+        <v>368</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>373</v>
+      <c r="A8" s="3" t="s">
+        <v>374</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>259</v>
+      <c r="A10" s="3" t="s">
+        <v>260</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>384</v>
+      <c r="A12" s="3" t="s">
+        <v>385</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>101</v>
+      <c r="A13" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>388</v>
+      <c r="A14" s="3" t="s">
+        <v>389</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>392</v>
+      <c r="A16" s="3" t="s">
+        <v>393</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>396</v>
+      <c r="A18" s="3" t="s">
+        <v>397</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2847,120 +2855,120 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>402</v>
       </c>
+      <c r="C4" s="4" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>403</v>
+      <c r="A5" s="3" t="s">
+        <v>404</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>408</v>
+      <c r="A7" s="3" t="s">
+        <v>409</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>412</v>
+      <c r="A9" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>415</v>
-      </c>
       <c r="C11" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2991,72 +2999,72 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>33</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="52" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="52" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3089,7 +3097,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3097,24 +3105,24 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>49</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3122,13 +3130,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3136,13 +3144,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3150,13 +3158,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3164,13 +3172,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3178,13 +3186,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3192,13 +3200,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3206,13 +3214,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3220,13 +3228,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3234,13 +3242,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3248,13 +3256,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3262,13 +3270,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3276,13 +3284,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3290,13 +3298,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3304,13 +3312,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3318,13 +3326,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3332,13 +3340,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3346,13 +3354,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3360,13 +3368,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3374,13 +3382,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3388,13 +3396,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3402,13 +3410,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3416,13 +3424,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3430,13 +3438,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3444,18 +3452,18 @@
         <v>24</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -3487,109 +3495,109 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
+      <c r="B4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>103</v>
+      <c r="A5" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>109</v>
+      <c r="A7" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>115</v>
+      <c r="A9" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>121</v>
+      <c r="A11" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -3619,73 +3627,73 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>128</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" s="14"/>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B12" s="20"/>
     </row>
@@ -3716,157 +3724,157 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>144</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -3896,127 +3904,127 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>128</v>
+      <c r="B4" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -4048,120 +4056,120 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>198</v>
       </c>
+      <c r="C4" s="4" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>199</v>
+      <c r="A5" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>205</v>
+      <c r="A7" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>209</v>
+      <c r="A9" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>214</v>
+      <c r="A11" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -4192,116 +4200,116 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>222</v>
       </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="5" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>223</v>
+      <c r="A5" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>229</v>
+      <c r="A7" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>235</v>
+      <c r="A9" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>241</v>
+      <c r="A11" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
